--- a/data/trans_orig/P05A06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A06-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2012</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2012 (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>306257</t>
+          <t>306719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>345485</t>
+          <t>344285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>287255</t>
+          <t>285514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>325768</t>
+          <t>321841</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>604495</t>
+          <t>602796</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>657015</t>
+          <t>658031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93751</t>
+          <t>94212</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130365</t>
+          <t>131653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89688</t>
+          <t>93311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126992</t>
+          <t>128523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>195433</t>
+          <t>194452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248825</t>
+          <t>247956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23342</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>19073</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39648</t>
+          <t>41664</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>464892</t>
+          <t>467992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>513848</t>
+          <t>515127</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>410215</t>
+          <t>406403</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455964</t>
+          <t>452583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>891791</t>
+          <t>890494</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>956457</t>
+          <t>958280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,08%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144637</t>
+          <t>143248</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>190103</t>
+          <t>187794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>134884</t>
+          <t>137153</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>181050</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>290498</t>
+          <t>289420</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>352978</t>
+          <t>352952</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>17744</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37951</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30530</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35535</t>
+          <t>34771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61834</t>
+          <t>62760</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>466949</t>
+          <t>468978</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>515740</t>
+          <t>516876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>489067</t>
+          <t>489204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>535635</t>
+          <t>537780</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>970942</t>
+          <t>973246</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1039923</t>
+          <t>1038391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138745</t>
+          <t>138377</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186327</t>
+          <t>183328</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146840</t>
+          <t>144607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193535</t>
+          <t>192394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>295465</t>
+          <t>295165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361104</t>
+          <t>359989</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32992</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37023</t>
+          <t>37663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33818</t>
+          <t>35368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63114</t>
+          <t>63113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>406048</t>
+          <t>406175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>456011</t>
+          <t>457475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>401884</t>
+          <t>401706</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>449783</t>
+          <t>449238</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>825148</t>
+          <t>820901</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>892812</t>
+          <t>888861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135527</t>
+          <t>137021</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>184031</t>
+          <t>185019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137794</t>
+          <t>137678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183714</t>
+          <t>183625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>285384</t>
+          <t>288512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>350972</t>
+          <t>353071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34596</t>
+          <t>35792</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15408</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39150</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33740</t>
+          <t>34057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63763</t>
+          <t>64672</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257611</t>
+          <t>254457</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298957</t>
+          <t>297421</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>290850</t>
+          <t>291950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>332571</t>
+          <t>331968</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>563314</t>
+          <t>561730</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>620132</t>
+          <t>619571</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>105009</t>
+          <t>104295</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>144800</t>
+          <t>143424</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>98605</t>
+          <t>98300</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>136717</t>
+          <t>136168</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>213274</t>
+          <t>214991</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>268741</t>
+          <t>271224</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16867</t>
+          <t>16842</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37413</t>
+          <t>38077</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25828</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>30099</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56653</t>
+          <t>56152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>202408</t>
+          <t>204397</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>237193</t>
+          <t>237483</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>223552</t>
+          <t>222187</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>256631</t>
+          <t>257987</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>434867</t>
+          <t>438395</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>485854</t>
+          <t>485851</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54715</t>
+          <t>52647</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86714</t>
+          <t>83929</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85567</t>
+          <t>83342</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117884</t>
+          <t>118390</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>146287</t>
+          <t>146075</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192757</t>
+          <t>191395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27117</t>
+          <t>25937</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17885</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38942</t>
+          <t>39891</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>170809</t>
+          <t>168554</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>197330</t>
+          <t>197677</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>260063</t>
+          <t>260426</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>297753</t>
+          <t>296245</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>441351</t>
+          <t>438676</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>486731</t>
+          <t>485632</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44410</t>
+          <t>44212</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70496</t>
+          <t>72171</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>82760</t>
+          <t>82753</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118284</t>
+          <t>118141</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>135241</t>
+          <t>135201</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>179384</t>
+          <t>179649</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2370677</t>
+          <t>2373160</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2484371</t>
+          <t>2480058</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2448334</t>
+          <t>2451318</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2564878</t>
+          <t>2558730</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4860721</t>
+          <t>4862065</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5018440</t>
+          <t>5015343</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>794985</t>
+          <t>796370</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>901057</t>
+          <t>895318</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>855530</t>
+          <t>863626</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>961751</t>
+          <t>967037</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1680810</t>
+          <t>1683984</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1827751</t>
+          <t>1830193</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>111618</t>
+          <t>113910</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>158155</t>
+          <t>159441</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>99266</t>
+          <t>97803</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>143646</t>
+          <t>141059</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>225439</t>
+          <t>221422</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>285568</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2016</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>311861</t>
+          <t>311144</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>345524</t>
+          <t>345815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>281914</t>
+          <t>283038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>313855</t>
+          <t>314703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>602261</t>
+          <t>606340</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>650552</t>
+          <t>650958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58052</t>
+          <t>56998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90064</t>
+          <t>89692</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62884</t>
+          <t>61997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93016</t>
+          <t>92583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129272</t>
+          <t>128485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>175371</t>
+          <t>171078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19122</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39257</t>
+          <t>39574</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408861</t>
+          <t>409971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451793</t>
+          <t>452876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>401802</t>
+          <t>403041</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>440328</t>
+          <t>441902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>824764</t>
+          <t>823144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>881488</t>
+          <t>881757</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111660</t>
+          <t>113183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153348</t>
+          <t>153031</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>102074</t>
+          <t>101920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>138955</t>
+          <t>140587</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>225556</t>
+          <t>227580</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>280689</t>
+          <t>282757</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36518</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31362</t>
+          <t>29874</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56579</t>
+          <t>55447</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>505323</t>
+          <t>506823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>548274</t>
+          <t>548676</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>484192</t>
+          <t>484210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>526863</t>
+          <t>527770</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1006834</t>
+          <t>1005391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1062841</t>
+          <t>1063246</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99704</t>
+          <t>100100</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140620</t>
+          <t>139936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111001</t>
+          <t>109416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152472</t>
+          <t>150549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>221117</t>
+          <t>222470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>277622</t>
+          <t>275417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>13281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29948</t>
+          <t>30559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29903</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53391</t>
+          <t>54436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>455859</t>
+          <t>456865</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>502787</t>
+          <t>501228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>480762</t>
+          <t>483275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>525979</t>
+          <t>524072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>956887</t>
+          <t>953343</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1016225</t>
+          <t>1017563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117998</t>
+          <t>117693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>162307</t>
+          <t>160070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97615</t>
+          <t>98735</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139994</t>
+          <t>138226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225422</t>
+          <t>227751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>283429</t>
+          <t>286347</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34908</t>
+          <t>34699</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31962</t>
+          <t>30875</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30604</t>
+          <t>32023</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56864</t>
+          <t>59779</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>337184</t>
+          <t>338296</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>377093</t>
+          <t>376514</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>340608</t>
+          <t>337553</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>382860</t>
+          <t>380165</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>692880</t>
+          <t>689209</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>749855</t>
+          <t>747908</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83743</t>
+          <t>83982</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>120772</t>
+          <t>120671</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>88327</t>
+          <t>90468</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>127217</t>
+          <t>129186</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>183115</t>
+          <t>182324</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>235258</t>
+          <t>236802</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30843</t>
+          <t>29251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34964</t>
+          <t>34696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>28858</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56518</t>
+          <t>56486</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>236615</t>
+          <t>238091</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>267875</t>
+          <t>268572</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>258335</t>
+          <t>257919</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>294577</t>
+          <t>292957</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>506972</t>
+          <t>507143</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>554409</t>
+          <t>551475</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53085</t>
+          <t>53053</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81829</t>
+          <t>80888</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70193</t>
+          <t>72585</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105219</t>
+          <t>104267</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130893</t>
+          <t>133492</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>179043</t>
+          <t>176027</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21451</t>
+          <t>23829</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33649</t>
+          <t>35091</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>181883</t>
+          <t>181830</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207259</t>
+          <t>207430</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>283588</t>
+          <t>283656</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>320899</t>
+          <t>323233</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>477614</t>
+          <t>476713</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>521812</t>
+          <t>521541</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41851</t>
+          <t>40904</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>66579</t>
+          <t>65226</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>62845</t>
+          <t>60542</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>98027</t>
+          <t>98466</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>110584</t>
+          <t>111105</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>151683</t>
+          <t>153025</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12448</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>25167</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32098</t>
+          <t>31838</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2526537</t>
+          <t>2530597</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2624790</t>
+          <t>2631855</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2616736</t>
+          <t>2625532</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2725308</t>
+          <t>2731399</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5180940</t>
+          <t>5180660</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5324212</t>
+          <t>5323665</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>636959</t>
+          <t>634101</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>731125</t>
+          <t>727126</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>671500</t>
+          <t>667810</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>772633</t>
+          <t>768259</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1333673</t>
+          <t>1329451</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1465255</t>
+          <t>1472085</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>97728</t>
+          <t>98658</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>142097</t>
+          <t>141005</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>97066</t>
+          <t>98995</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>141938</t>
+          <t>141886</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>206895</t>
+          <t>207919</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>269308</t>
+          <t>270301</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2023</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>299072</t>
+          <t>299354</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>350891</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>208990</t>
+          <t>207731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>252318</t>
+          <t>251466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>524504</t>
+          <t>526367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>594564</t>
+          <t>593564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26102</t>
+          <t>25949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67085</t>
+          <t>64658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39066</t>
+          <t>39332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77682</t>
+          <t>79676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71328</t>
+          <t>74782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130980</t>
+          <t>130250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -8724,12 +8724,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53255</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>39237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33661</t>
+          <t>32327</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78275</t>
+          <t>81628</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>331315</t>
+          <t>332484</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>370260</t>
+          <t>372195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>414136</t>
+          <t>411261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>464169</t>
+          <t>462666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,47 +9004,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>80,31%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>90,35%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>788301</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>756666</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>823292</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>84,25%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>80,87%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>90,64%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>788301</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>759155</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>824951</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>84,25%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>81,14%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,99%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32705</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65320</t>
+          <t>64143</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34635</t>
+          <t>33927</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75719</t>
+          <t>76338</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>74711</t>
+          <t>77410</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>127098</t>
+          <t>131069</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39185</t>
+          <t>40532</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32930</t>
+          <t>32092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29916</t>
+          <t>31433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63728</t>
+          <t>64195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>424282</t>
+          <t>425014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>460106</t>
+          <t>461053</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>488268</t>
+          <t>488737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>527102</t>
+          <t>527473</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>922531</t>
+          <t>923935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>976620</t>
+          <t>977553</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41861</t>
+          <t>41730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69858</t>
+          <t>72319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72071</t>
+          <t>72994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92049</t>
+          <t>92288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136090</t>
+          <t>134710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22195</t>
+          <t>21206</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45750</t>
+          <t>44781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18602</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37948</t>
+          <t>36916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45598</t>
+          <t>44699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75364</t>
+          <t>75256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>707866</t>
+          <t>706836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>836300</t>
+          <t>834280</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>583820</t>
+          <t>582835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>619631</t>
+          <t>618262</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1309943</t>
+          <t>1312215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1468390</t>
+          <t>1453350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>43462</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150824</t>
+          <t>148247</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70989</t>
+          <t>71753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103778</t>
+          <t>103718</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105196</t>
+          <t>112902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232324</t>
+          <t>234235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30869</t>
+          <t>31082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26751</t>
+          <t>24829</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61176</t>
+          <t>59421</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10322,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>449399</t>
+          <t>449057</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>481569</t>
+          <t>482372</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>420188</t>
+          <t>420764</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>448112</t>
+          <t>449246</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>879646</t>
+          <t>880449</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>922466</t>
+          <t>924966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62742</t>
+          <t>62460</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92650</t>
+          <t>94274</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76180</t>
+          <t>74669</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102126</t>
+          <t>101273</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10500,17 +10500,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>165800</t>
+          <t>165799</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>146397</t>
+          <t>145351</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>185796</t>
+          <t>186626</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>26602</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15099</t>
+          <t>15267</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>29305</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29831</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49984</t>
+          <t>50481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -10726,17 +10726,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1107161</t>
+          <t>1107160</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1107161</t>
+          <t>1107160</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1107161</t>
+          <t>1107160</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10778,12 +10778,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>298710</t>
+          <t>298375</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>320998</t>
+          <t>320481</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>498671</t>
+          <t>499023</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>582840</t>
+          <t>580595</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>809634</t>
+          <t>810143</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>908231</t>
+          <t>911269</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50481</t>
+          <t>49848</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>20939</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87328</t>
+          <t>85967</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48347</t>
+          <t>46079</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>123726</t>
+          <t>124186</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -11004,12 +11004,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23629</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40760</t>
+          <t>41235</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>228429</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>249028</t>
+          <t>248288</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>338390</t>
+          <t>338255</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>360654</t>
+          <t>360694</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>573910</t>
+          <t>574282</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>602844</t>
+          <t>604983</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27550</t>
+          <t>27904</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46535</t>
+          <t>45968</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>49145</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69693</t>
+          <t>69383</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>81499</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>109554</t>
+          <t>108434</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20494</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>29176</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2841358</t>
+          <t>2847254</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3029487</t>
+          <t>3023150</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3030929</t>
+          <t>3030764</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3196334</t>
+          <t>3201188</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5901152</t>
+          <t>5907290</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6136752</t>
+          <t>6173974</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>309567</t>
+          <t>310272</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>447893</t>
+          <t>448554</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>383699</t>
+          <t>379159</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>514116</t>
+          <t>511904</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>761411</t>
+          <t>740484</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>946380</t>
+          <t>941858</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>109900</t>
+          <t>111463</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>181725</t>
+          <t>179065</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>117127</t>
+          <t>117452</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>175257</t>
+          <t>171050</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>249303</t>
+          <t>239972</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>334324</t>
+          <t>330670</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A06-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>306719</t>
+          <t>306975</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>344285</t>
+          <t>344952</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>285514</t>
+          <t>284995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>321841</t>
+          <t>322379</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>602796</t>
+          <t>603720</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>658031</t>
+          <t>658672</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94212</t>
+          <t>92616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131653</t>
+          <t>130085</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93311</t>
+          <t>92106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128523</t>
+          <t>127987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>194452</t>
+          <t>196216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247956</t>
+          <t>249286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23646</t>
+          <t>22146</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41664</t>
+          <t>40274</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467992</t>
+          <t>467397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>515127</t>
+          <t>514662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>406403</t>
+          <t>409450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452583</t>
+          <t>454598</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>890494</t>
+          <t>893083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>958280</t>
+          <t>957392</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,01%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>143248</t>
+          <t>142839</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>187794</t>
+          <t>187675</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>137153</t>
+          <t>137388</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181050</t>
+          <t>181439</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>289420</t>
+          <t>289633</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>352952</t>
+          <t>353163</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>38272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12990</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>32412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34771</t>
+          <t>34948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62760</t>
+          <t>62754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>468978</t>
+          <t>468453</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>516876</t>
+          <t>515905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>489204</t>
+          <t>488791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>537780</t>
+          <t>536041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>973246</t>
+          <t>971927</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1038391</t>
+          <t>1043275</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,49%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138377</t>
+          <t>139434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>183328</t>
+          <t>183967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>144607</t>
+          <t>146923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192394</t>
+          <t>193292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>295165</t>
+          <t>296141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359989</t>
+          <t>359637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32914</t>
+          <t>33301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37663</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35368</t>
+          <t>35232</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63113</t>
+          <t>63493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>406175</t>
+          <t>404833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>457475</t>
+          <t>457820</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>401706</t>
+          <t>401175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>449238</t>
+          <t>450302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>820901</t>
+          <t>821642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>888861</t>
+          <t>890358</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,73%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137021</t>
+          <t>133702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185019</t>
+          <t>181674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137678</t>
+          <t>139349</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183625</t>
+          <t>185150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>288512</t>
+          <t>288037</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353071</t>
+          <t>354619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35792</t>
+          <t>35396</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35898</t>
+          <t>37943</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34057</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64672</t>
+          <t>65387</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254457</t>
+          <t>256301</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297421</t>
+          <t>296833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>291950</t>
+          <t>293894</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>331968</t>
+          <t>336243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>561730</t>
+          <t>560184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>619571</t>
+          <t>619278</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104295</t>
+          <t>106907</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>143424</t>
+          <t>144419</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>98300</t>
+          <t>94842</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>136168</t>
+          <t>134071</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>214991</t>
+          <t>211204</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>271224</t>
+          <t>269797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16842</t>
+          <t>17653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38077</t>
+          <t>37723</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>24315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30099</t>
+          <t>31092</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56152</t>
+          <t>56872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>204397</t>
+          <t>203982</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>237483</t>
+          <t>237869</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>222187</t>
+          <t>221475</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>257987</t>
+          <t>257075</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>438395</t>
+          <t>440488</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>485851</t>
+          <t>487702</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,15%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52647</t>
+          <t>52872</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83929</t>
+          <t>85126</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>83342</t>
+          <t>85296</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118390</t>
+          <t>120014</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>146075</t>
+          <t>144958</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>191395</t>
+          <t>190857</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18889</t>
+          <t>18693</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18008</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39891</t>
+          <t>39769</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>168554</t>
+          <t>168973</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>197677</t>
+          <t>198225</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>260426</t>
+          <t>261950</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>296245</t>
+          <t>298201</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>438676</t>
+          <t>439209</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>485632</t>
+          <t>485378</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44212</t>
+          <t>43524</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>72171</t>
+          <t>70602</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>82753</t>
+          <t>81623</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118141</t>
+          <t>116493</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>135201</t>
+          <t>134783</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>179649</t>
+          <t>181180</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12976</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13951</t>
+          <t>14809</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2373160</t>
+          <t>2370101</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2480058</t>
+          <t>2476910</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2451318</t>
+          <t>2446841</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2558730</t>
+          <t>2562951</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4862065</t>
+          <t>4861156</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5015343</t>
+          <t>5014272</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>796370</t>
+          <t>800218</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>895318</t>
+          <t>903311</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>863626</t>
+          <t>858300</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>967037</t>
+          <t>967731</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1683984</t>
+          <t>1685004</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1830193</t>
+          <t>1831957</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>113910</t>
+          <t>110594</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>159441</t>
+          <t>159516</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>97803</t>
+          <t>96256</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>141059</t>
+          <t>139641</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>221422</t>
+          <t>219098</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>285568</t>
+          <t>286805</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>311144</t>
+          <t>312678</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>345815</t>
+          <t>345736</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>283038</t>
+          <t>281369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>314703</t>
+          <t>315216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>606340</t>
+          <t>602267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>650958</t>
+          <t>652260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56998</t>
+          <t>57634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>89105</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61997</t>
+          <t>61643</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92583</t>
+          <t>93000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128485</t>
+          <t>127287</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171078</t>
+          <t>174012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>24839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18208</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39574</t>
+          <t>40596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409971</t>
+          <t>408810</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>452876</t>
+          <t>452403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>403041</t>
+          <t>400867</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>441902</t>
+          <t>442711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>823144</t>
+          <t>827183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>881757</t>
+          <t>880241</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113183</t>
+          <t>113266</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153031</t>
+          <t>154563</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101920</t>
+          <t>102629</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>140587</t>
+          <t>142718</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>227580</t>
+          <t>227627</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>282757</t>
+          <t>280704</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>34733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>27776</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29874</t>
+          <t>31903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55447</t>
+          <t>57903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>506823</t>
+          <t>506848</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>548676</t>
+          <t>546191</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>484210</t>
+          <t>483907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>527770</t>
+          <t>527141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1005391</t>
+          <t>1000623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1063246</t>
+          <t>1062714</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100100</t>
+          <t>101494</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139936</t>
+          <t>140432</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109416</t>
+          <t>109838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150549</t>
+          <t>152158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222470</t>
+          <t>224086</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275417</t>
+          <t>281928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13281</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30559</t>
+          <t>31163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>13051</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30502</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>29564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54436</t>
+          <t>54188</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>456865</t>
+          <t>460173</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>501228</t>
+          <t>503428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>483275</t>
+          <t>482516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>524072</t>
+          <t>527229</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>953343</t>
+          <t>951022</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1017563</t>
+          <t>1014020</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117693</t>
+          <t>116401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160070</t>
+          <t>157959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98735</t>
+          <t>98196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138226</t>
+          <t>140093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227751</t>
+          <t>227896</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286347</t>
+          <t>287150</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34699</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30875</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32023</t>
+          <t>31034</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59779</t>
+          <t>57366</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>338296</t>
+          <t>337876</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>376514</t>
+          <t>376844</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>337553</t>
+          <t>341721</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>380165</t>
+          <t>381183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>689209</t>
+          <t>688371</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>747908</t>
+          <t>748200</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83982</t>
+          <t>83198</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>120671</t>
+          <t>119894</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>90468</t>
+          <t>91551</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>129186</t>
+          <t>128676</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>182324</t>
+          <t>183023</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>236802</t>
+          <t>238082</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29251</t>
+          <t>29086</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34696</t>
+          <t>36079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56486</t>
+          <t>58208</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>238091</t>
+          <t>236113</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>268572</t>
+          <t>267562</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>257919</t>
+          <t>258218</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>292957</t>
+          <t>293605</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>507143</t>
+          <t>505961</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>551475</t>
+          <t>551929</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,16%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53053</t>
+          <t>53007</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80888</t>
+          <t>82529</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72585</t>
+          <t>71211</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>104267</t>
+          <t>105622</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>133492</t>
+          <t>133584</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176027</t>
+          <t>179290</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18301</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23829</t>
+          <t>21556</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>14749</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35091</t>
+          <t>35837</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>182463</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207430</t>
+          <t>206097</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>283656</t>
+          <t>281690</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>323233</t>
+          <t>321987</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>476713</t>
+          <t>473992</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>521541</t>
+          <t>522583</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,33%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40904</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>65226</t>
+          <t>65767</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>60542</t>
+          <t>62587</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>98466</t>
+          <t>99289</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>111105</t>
+          <t>109191</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>153025</t>
+          <t>155577</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25167</t>
+          <t>24895</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>12433</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31838</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2530597</t>
+          <t>2524371</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2631855</t>
+          <t>2622349</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2625532</t>
+          <t>2624186</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2731399</t>
+          <t>2726526</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5180660</t>
+          <t>5177574</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5323665</t>
+          <t>5315483</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>634101</t>
+          <t>636677</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>727126</t>
+          <t>729294</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>667810</t>
+          <t>669863</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>768259</t>
+          <t>766943</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1329451</t>
+          <t>1340613</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1472085</t>
+          <t>1476494</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>98658</t>
+          <t>98144</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>141005</t>
+          <t>139187</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>98995</t>
+          <t>100001</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>141886</t>
+          <t>143598</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>207527</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>270301</t>
+          <t>269485</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -8493,32 +8493,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>328560</t>
+          <t>333090</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>299354</t>
+          <t>305807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>350891</t>
+          <t>355074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8528,32 +8528,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>232765</t>
+          <t>272066</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>207731</t>
+          <t>248792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>251466</t>
+          <t>294598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8563,32 +8563,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>561325</t>
+          <t>605156</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>526367</t>
+          <t>568064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>593564</t>
+          <t>636521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -8606,32 +8606,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>47080</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25949</t>
+          <t>29922</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64658</t>
+          <t>71321</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8641,32 +8641,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56780</t>
+          <t>61668</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39332</t>
+          <t>41444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79676</t>
+          <t>84098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8676,32 +8676,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>99890</t>
+          <t>108748</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74782</t>
+          <t>82418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130250</t>
+          <t>140118</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -8719,32 +8719,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>27623</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51147</t>
+          <t>48534</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8754,32 +8754,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>28778</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39237</t>
+          <t>44734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8789,32 +8789,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>51972</t>
+          <t>56400</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32327</t>
+          <t>37926</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81628</t>
+          <t>84555</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -8832,17 +8832,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8867,17 +8867,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8902,17 +8902,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8949,32 +8949,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>353605</t>
+          <t>395240</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>332484</t>
+          <t>371468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372195</t>
+          <t>413723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8984,32 +8984,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>434696</t>
+          <t>410437</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>411261</t>
+          <t>389433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462666</t>
+          <t>427266</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9019,32 +9019,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>788301</t>
+          <t>805677</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>756666</t>
+          <t>778223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>823292</t>
+          <t>832532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -9062,32 +9062,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45932</t>
+          <t>53733</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>38420</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64143</t>
+          <t>73833</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9097,32 +9097,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56537</t>
+          <t>64083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33927</t>
+          <t>49143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76338</t>
+          <t>82781</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9132,32 +9132,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>102469</t>
+          <t>117816</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>77410</t>
+          <t>95541</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>131069</t>
+          <t>142022</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -9175,32 +9175,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24010</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>17762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40532</t>
+          <t>44829</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9210,32 +9210,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>27213</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>17872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>38009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9245,32 +9245,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44870</t>
+          <t>55130</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31433</t>
+          <t>40905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64195</t>
+          <t>75024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -9288,17 +9288,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9323,17 +9323,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9405,32 +9405,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>443965</t>
+          <t>509926</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>425014</t>
+          <t>489230</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>461053</t>
+          <t>527973</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9440,32 +9440,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>505089</t>
+          <t>518994</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>488737</t>
+          <t>501465</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>527473</t>
+          <t>533777</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9475,32 +9475,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>949053</t>
+          <t>1028920</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>923935</t>
+          <t>1001997</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>977553</t>
+          <t>1052136</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -9518,32 +9518,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54249</t>
+          <t>65738</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41730</t>
+          <t>50661</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72319</t>
+          <t>85087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
+          <t>70778</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>58626</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>43194</t>
-        </is>
-      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72994</t>
+          <t>85198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9588,32 +9588,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>112875</t>
+          <t>136517</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92288</t>
+          <t>114814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134710</t>
+          <t>157532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -9631,32 +9631,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32039</t>
+          <t>37219</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21206</t>
+          <t>25091</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44781</t>
+          <t>51041</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9666,32 +9666,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27397</t>
+          <t>31938</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>23327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36916</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9701,32 +9701,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>59436</t>
+          <t>69156</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>55829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75256</t>
+          <t>86564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -9744,17 +9744,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>530253</t>
+          <t>612883</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>530253</t>
+          <t>612883</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>530253</t>
+          <t>612883</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9779,17 +9779,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621710</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621710</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621710</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9814,17 +9814,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1121364</t>
+          <t>1234593</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1121364</t>
+          <t>1234593</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1121364</t>
+          <t>1234593</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9861,32 +9861,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>765677</t>
+          <t>573767</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>706836</t>
+          <t>552488</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>834280</t>
+          <t>593888</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9896,32 +9896,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>599302</t>
+          <t>608943</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>582835</t>
+          <t>592620</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>618262</t>
+          <t>624676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9931,32 +9931,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1364978</t>
+          <t>1182710</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1312215</t>
+          <t>1152515</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1453350</t>
+          <t>1206610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -9974,32 +9974,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>99958</t>
+          <t>103200</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43462</t>
+          <t>85223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148247</t>
+          <t>123209</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10009,32 +10009,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>88085</t>
+          <t>97273</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71753</t>
+          <t>81723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103718</t>
+          <t>111270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10044,32 +10044,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>188043</t>
+          <t>200473</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112902</t>
+          <t>176800</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>234235</t>
+          <t>226734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -10087,32 +10087,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21077</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35588</t>
+          <t>34517</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10122,32 +10122,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23208</t>
+          <t>27173</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31082</t>
+          <t>36704</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10157,32 +10157,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>44285</t>
+          <t>49725</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24829</t>
+          <t>37668</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59421</t>
+          <t>64071</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -10200,17 +10200,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10235,17 +10235,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>710595</t>
+          <t>733389</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>710595</t>
+          <t>733389</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>710595</t>
+          <t>733389</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10270,17 +10270,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1597306</t>
+          <t>1432908</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1597306</t>
+          <t>1432908</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1597306</t>
+          <t>1432908</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10317,32 +10317,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>466814</t>
+          <t>509299</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>449057</t>
+          <t>491667</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>482372</t>
+          <t>525132</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10352,32 +10352,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>435393</t>
+          <t>483774</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>420764</t>
+          <t>468190</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>449246</t>
+          <t>498109</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10387,32 +10387,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>902207</t>
+          <t>993072</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>880449</t>
+          <t>971731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>924966</t>
+          <t>1017663</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -10430,32 +10430,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>76895</t>
+          <t>80506</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62460</t>
+          <t>65442</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94274</t>
+          <t>97406</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10465,32 +10465,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>88904</t>
+          <t>98970</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74669</t>
+          <t>86551</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101273</t>
+          <t>113722</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10500,32 +10500,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>165799</t>
+          <t>179476</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>145351</t>
+          <t>158920</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>186626</t>
+          <t>202238</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -10543,32 +10543,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>17524</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26602</t>
+          <t>29551</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10578,17 +10578,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21630</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29305</t>
+          <t>33384</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10613,32 +10613,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>39154</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30169</t>
+          <t>33745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50481</t>
+          <t>56170</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -10656,17 +10656,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>545927</t>
+          <t>606744</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>545927</t>
+          <t>606744</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>545927</t>
+          <t>606744</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10726,17 +10726,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1107160</t>
+          <t>1216090</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1107160</t>
+          <t>1216090</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1107160</t>
+          <t>1216090</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10773,27 +10773,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>310348</t>
+          <t>343615</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>298375</t>
+          <t>329920</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>320481</t>
+          <t>354154</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -10808,32 +10808,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>538158</t>
+          <t>362091</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>499023</t>
+          <t>349993</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>580595</t>
+          <t>372596</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10843,32 +10843,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>848506</t>
+          <t>705706</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>810143</t>
+          <t>687953</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>911269</t>
+          <t>722621</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -10886,17 +10886,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>39961</t>
+          <t>44174</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31139</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49848</t>
+          <t>56146</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10921,32 +10921,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>54442</t>
+          <t>60033</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20939</t>
+          <t>50191</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85967</t>
+          <t>71345</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10956,32 +10956,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>94403</t>
+          <t>104207</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46079</t>
+          <t>89616</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>124186</t>
+          <t>121464</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -10999,32 +10999,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15043</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11034,32 +11034,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>21595</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11069,32 +11069,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>29081</t>
+          <t>31129</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41235</t>
+          <t>40606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -11112,17 +11112,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>365352</t>
+          <t>403747</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>365352</t>
+          <t>403747</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>365352</t>
+          <t>403747</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11147,17 +11147,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>606638</t>
+          <t>437295</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>606638</t>
+          <t>437295</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>606638</t>
+          <t>437295</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11182,17 +11182,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>971990</t>
+          <t>841042</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>971990</t>
+          <t>841042</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>971990</t>
+          <t>841042</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11229,32 +11229,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>239188</t>
+          <t>261416</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>228429</t>
+          <t>250015</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>248288</t>
+          <t>271152</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11264,32 +11264,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>350286</t>
+          <t>380185</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>338255</t>
+          <t>365871</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>360694</t>
+          <t>391717</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11299,32 +11299,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>589475</t>
+          <t>641601</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>574282</t>
+          <t>624982</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>604983</t>
+          <t>658377</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -11342,32 +11342,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>36167</t>
+          <t>40736</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27904</t>
+          <t>31553</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45968</t>
+          <t>51622</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11377,32 +11377,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>58273</t>
+          <t>64514</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47876</t>
+          <t>53697</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69383</t>
+          <t>76645</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11412,32 +11412,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>94440</t>
+          <t>105250</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>80014</t>
+          <t>90812</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>108434</t>
+          <t>120297</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -11455,32 +11455,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11490,32 +11490,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21134</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11525,32 +11525,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>21525</t>
+          <t>24548</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>17829</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29176</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -11568,17 +11568,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282359</t>
+          <t>309775</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282359</t>
+          <t>309775</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282359</t>
+          <t>309775</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11603,17 +11603,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>423080</t>
+          <t>461624</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>423080</t>
+          <t>461624</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>423080</t>
+          <t>461624</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11638,17 +11638,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>705439</t>
+          <t>771399</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>705439</t>
+          <t>771399</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>705439</t>
+          <t>771399</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11685,32 +11685,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2908157</t>
+          <t>2926353</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2847254</t>
+          <t>2870584</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3023150</t>
+          <t>2974759</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11720,32 +11720,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3095688</t>
+          <t>3036490</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3030764</t>
+          <t>2985912</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3201188</t>
+          <t>3078779</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11755,32 +11755,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>6003845</t>
+          <t>5962844</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5907290</t>
+          <t>5897423</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6173974</t>
+          <t>6029137</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -11798,32 +11798,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>396272</t>
+          <t>435167</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>310272</t>
+          <t>394162</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>482171</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11833,32 +11833,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>461647</t>
+          <t>517320</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>379159</t>
+          <t>480748</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>511904</t>
+          <t>564479</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11868,32 +11868,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>857919</t>
+          <t>952487</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>740484</t>
+          <t>892278</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>941858</t>
+          <t>1012514</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -11911,32 +11911,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>145015</t>
+          <t>158433</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>111463</t>
+          <t>133446</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>179065</t>
+          <t>193593</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11946,32 +11946,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>145308</t>
+          <t>171197</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>117452</t>
+          <t>146893</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>171050</t>
+          <t>198268</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11981,32 +11981,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>290323</t>
+          <t>329630</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>239972</t>
+          <t>293762</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>330670</t>
+          <t>370437</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -12024,17 +12024,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3449443</t>
+          <t>3519953</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3449443</t>
+          <t>3519953</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3449443</t>
+          <t>3519953</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12059,17 +12059,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3702643</t>
+          <t>3725007</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3702643</t>
+          <t>3725007</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3702643</t>
+          <t>3725007</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12094,17 +12094,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7152086</t>
+          <t>7244961</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7152086</t>
+          <t>7244961</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7152086</t>
+          <t>7244961</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
